--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.91444373926734</v>
+        <v>3.236097107630944</v>
       </c>
       <c r="D2" t="n">
-        <v>71.75886703491476</v>
+        <v>11.66081589317365</v>
       </c>
       <c r="E2" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F2" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.32219959312593</v>
+        <v>7.039857433882964</v>
       </c>
       <c r="D3" t="n">
-        <v>45.80953018057524</v>
+        <v>7.444048654343478</v>
       </c>
       <c r="E3" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F3" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.14362786139428</v>
+        <v>3.598339527476571</v>
       </c>
       <c r="D4" t="n">
-        <v>24.99566196549774</v>
+        <v>4.061795069393382</v>
       </c>
       <c r="E4" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F4" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.62266264053326</v>
+        <v>6.276182679086656</v>
       </c>
       <c r="D5" t="n">
-        <v>55.64239914394857</v>
+        <v>9.041889860891642</v>
       </c>
       <c r="E5" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F5" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.32200209201343</v>
+        <v>7.202325339952183</v>
       </c>
       <c r="D6" t="n">
-        <v>54.89710276881197</v>
+        <v>8.920779199931946</v>
       </c>
       <c r="E6" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F6" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.97339414207993</v>
+        <v>2.270676548087988</v>
       </c>
       <c r="D7" t="n">
-        <v>14.15138599074697</v>
+        <v>2.299600223496383</v>
       </c>
       <c r="E7" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F7" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.496519214923346</v>
+        <v>1.543184372425044</v>
       </c>
       <c r="D8" t="n">
-        <v>9.058127307185746</v>
+        <v>1.471945687417684</v>
       </c>
       <c r="E8" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F8" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.9164338901763</v>
+        <v>2.423920507153649</v>
       </c>
       <c r="D9" t="n">
-        <v>15.79936490536548</v>
+        <v>2.56739679712189</v>
       </c>
       <c r="E9" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F9" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.28788168000227</v>
+        <v>2.321780773000369</v>
       </c>
       <c r="D10" t="n">
-        <v>13.18715061074555</v>
+        <v>2.142911974246151</v>
       </c>
       <c r="E10" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F10" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.55322666984006</v>
+        <v>2.85239933384901</v>
       </c>
       <c r="D11" t="n">
-        <v>15.11332699077573</v>
+        <v>2.455915636001056</v>
       </c>
       <c r="E11" t="n">
-        <v>12.44734044326932</v>
+        <v>2.022692822031264</v>
       </c>
       <c r="F11" t="n">
-        <v>21.56432432305257</v>
+        <v>3.504202702496043</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
